--- a/02_DIA_inicio_2026_analisis_assets/rbd_9736_escuela-basica-bernardo-o-higgins_nt1_nucleos.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9736_escuela-basica-bernardo-o-higgins_nt1_nucleos.xlsx
@@ -775,13 +775,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A92B841E-54A4-4429-AFAF-BE6A8CE90A25}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D07A17DC-F443-4E09-A002-95C0B3929648}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B9DDB7C-2B86-447F-B0E6-4E50EF7662C1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E95D32B8-BF3F-42F9-91EC-672964F0AEF3}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FCECA1FB-75E1-4D3D-AF7B-CCA9CEB0F66B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD01DA67-795C-4B43-A43A-5EEDFA0CC069}"/>
 </file>